--- a/LOCATION-SHEETS/MISSING-SHEETS.xlsx
+++ b/LOCATION-SHEETS/MISSING-SHEETS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10411"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10611"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ed/Documents/GitHub/rainfall-rescue/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ed/Documents/GitHub/rainfall-rescue/LOCATION-SHEETS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F203186C-55AB-9B48-865F-E462DD5F01DC}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF77B130-1A71-2949-A1BA-6AEB798E4615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1240" yWindow="780" windowWidth="27200" windowHeight="14880" xr2:uid="{BBF0E115-4142-CB48-B420-5D0EBD0E64F7}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="43">
   <si>
     <t>Station name</t>
   </si>
@@ -148,6 +148,21 @@
   </si>
   <si>
     <t>PONDERS END PUMPING STATION</t>
+  </si>
+  <si>
+    <t>SCARBOROUGH-SCALBY-ST-PHILIPS</t>
+  </si>
+  <si>
+    <t>GRIMSBY-RIBY</t>
+  </si>
+  <si>
+    <t>HULL-WW-FARNDALE-SEVEN</t>
+  </si>
+  <si>
+    <t>FILEY-VICARAGE</t>
+  </si>
+  <si>
+    <t>SIBSEY-IVYDENE</t>
   </si>
 </sst>
 </file>
@@ -704,7 +719,7 @@
         <v>24</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="C13" s="6">
         <v>3468</v>
@@ -718,7 +733,7 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>14</v>
@@ -760,7 +775,7 @@
         <v>22</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>23</v>
@@ -774,7 +789,7 @@
         <v>28</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="C18" s="6">
         <v>3407</v>
@@ -788,7 +803,7 @@
         <v>26</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>27</v>

--- a/LOCATION-SHEETS/MISSING-SHEETS.xlsx
+++ b/LOCATION-SHEETS/MISSING-SHEETS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ed/Documents/GitHub/rainfall-rescue/LOCATION-SHEETS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF77B130-1A71-2949-A1BA-6AEB798E4615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFAE810F-2818-8A4F-80BF-57DC68673905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1240" yWindow="780" windowWidth="27200" windowHeight="14880" xr2:uid="{BBF0E115-4142-CB48-B420-5D0EBD0E64F7}"/>
+    <workbookView xWindow="4800" yWindow="1660" windowWidth="27200" windowHeight="14880" xr2:uid="{BBF0E115-4142-CB48-B420-5D0EBD0E64F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="57">
   <si>
     <t>Station name</t>
   </si>
@@ -163,13 +163,55 @@
   </si>
   <si>
     <t>SIBSEY-IVYDENE</t>
+  </si>
+  <si>
+    <t>ATTENBOROUGH</t>
+  </si>
+  <si>
+    <t>Attenborough</t>
+  </si>
+  <si>
+    <t>2601</t>
+  </si>
+  <si>
+    <t>CARDIFF-WW-TROEDYRHIW</t>
+  </si>
+  <si>
+    <t>CARDIFF-WW-LLWYNON-RES</t>
+  </si>
+  <si>
+    <t>4148</t>
+  </si>
+  <si>
+    <t>3334</t>
+  </si>
+  <si>
+    <t>SKIPTON-BARDEN-RES</t>
+  </si>
+  <si>
+    <t>Cardiff Troedyrhiw WW</t>
+  </si>
+  <si>
+    <t>Cardiff Llyynon Reservoir WW</t>
+  </si>
+  <si>
+    <t>Skipton Barden Reservoir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apsley Mill </t>
+  </si>
+  <si>
+    <t>HEMEL-HEMPSTEAD-APSLEY-MILLS</t>
+  </si>
+  <si>
+    <t>920</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -184,6 +226,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="15"/>
+      <color rgb="FF646464"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -206,7 +254,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -222,6 +270,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -536,7 +585,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC75AAC6-CB18-4040-A1AE-A5995A9D3845}">
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="42.6640625" style="2" customWidth="1"/>
@@ -812,6 +861,105 @@
         <v>1950</v>
       </c>
     </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" s="4">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="4">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" s="4">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23" s="4">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1860</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="4">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="19" x14ac:dyDescent="0.2">
+      <c r="A26" s="7"/>
+    </row>
+    <row r="27" spans="1:4" ht="19" x14ac:dyDescent="0.2">
+      <c r="A27" s="7"/>
+    </row>
+    <row r="28" spans="1:4" ht="19" x14ac:dyDescent="0.2">
+      <c r="A28" s="7"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29"/>
+    </row>
+    <row r="30" spans="1:4" ht="19" x14ac:dyDescent="0.2">
+      <c r="A30" s="7"/>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D19">
     <sortCondition ref="D2:D19"/>

--- a/LOCATION-SHEETS/MISSING-SHEETS.xlsx
+++ b/LOCATION-SHEETS/MISSING-SHEETS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10611"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11113"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ed/Documents/GitHub/rainfall-rescue/LOCATION-SHEETS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFAE810F-2818-8A4F-80BF-57DC68673905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A531EDB6-A328-6946-B6CD-67B77AC1098C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4800" yWindow="1660" windowWidth="27200" windowHeight="14880" xr2:uid="{BBF0E115-4142-CB48-B420-5D0EBD0E64F7}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="59">
   <si>
     <t>Station name</t>
   </si>
@@ -205,6 +205,12 @@
   </si>
   <si>
     <t>920</t>
+  </si>
+  <si>
+    <t>Tomintoul</t>
+  </si>
+  <si>
+    <t>TOMINTOUL</t>
   </si>
 </sst>
 </file>
@@ -585,7 +591,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC75AAC6-CB18-4040-A1AE-A5995A9D3845}">
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="42.6640625" style="2" customWidth="1"/>
@@ -639,330 +645,342 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="D4" s="4">
-        <v>1870</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="D5" s="4">
-        <v>1880</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="6">
-        <v>2309</v>
+        <v>21</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="D6" s="4">
-        <v>1890</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="6">
-        <v>804</v>
+        <v>16</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="D7" s="4">
-        <v>1900</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="6">
-        <v>2667</v>
+        <v>58</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="D8" s="4">
-        <v>1910</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>3626</v>
+        <v>2309</v>
       </c>
       <c r="D9" s="4">
-        <v>1910</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>14</v>
+        <v>4</v>
+      </c>
+      <c r="C10" s="6">
+        <v>804</v>
       </c>
       <c r="D10" s="4">
-        <v>1910</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="C11" s="6">
-        <v>2651</v>
+        <v>2667</v>
       </c>
       <c r="D11" s="4">
-        <v>1920</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C12" s="6">
-        <v>890</v>
+        <v>3626</v>
       </c>
       <c r="D12" s="4">
-        <v>1920</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" s="6">
-        <v>3468</v>
+        <v>11</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="D13" s="4">
-        <v>1920</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>14</v>
       </c>
       <c r="D14" s="4">
-        <v>1920</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="D15" s="4">
-        <v>1920</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="6">
-        <v>4227</v>
+        <v>50</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>49</v>
       </c>
       <c r="D16" s="4">
-        <v>1930</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="D17" s="4">
-        <v>1930</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="C18" s="6">
-        <v>3407</v>
+        <v>2651</v>
       </c>
       <c r="D18" s="4">
-        <v>1930</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>27</v>
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>890</v>
       </c>
       <c r="D19" s="4">
-        <v>1950</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
+      </c>
+      <c r="C20" s="6">
+        <v>3468</v>
       </c>
       <c r="D20" s="4">
         <v>1920</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>14</v>
       </c>
       <c r="D21" s="4">
-        <v>1910</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="D22" s="4">
-        <v>1910</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>49</v>
+        <v>10</v>
+      </c>
+      <c r="C23" s="6">
+        <v>4227</v>
       </c>
       <c r="D23" s="4">
-        <v>1910</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+        <v>1930</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="19" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="D24" s="4">
-        <v>1860</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+        <v>1930</v>
+      </c>
+      <c r="E24" s="7"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>56</v>
+        <v>41</v>
+      </c>
+      <c r="C25" s="6">
+        <v>3407</v>
       </c>
       <c r="D25" s="4">
-        <v>1870</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="19" x14ac:dyDescent="0.2">
-      <c r="A26" s="7"/>
-    </row>
-    <row r="27" spans="1:4" ht="19" x14ac:dyDescent="0.2">
-      <c r="A27" s="7"/>
-    </row>
-    <row r="28" spans="1:4" ht="19" x14ac:dyDescent="0.2">
-      <c r="A28" s="7"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29"/>
-    </row>
-    <row r="30" spans="1:4" ht="19" x14ac:dyDescent="0.2">
+        <v>1930</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D26" s="4">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="19" x14ac:dyDescent="0.2">
       <c r="A30" s="7"/>
     </row>
+    <row r="31" spans="1:5" ht="19" x14ac:dyDescent="0.2">
+      <c r="A31" s="7"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32"/>
+    </row>
+    <row r="33" spans="1:1" ht="19" x14ac:dyDescent="0.2">
+      <c r="A33" s="7"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D19">
-    <sortCondition ref="D2:D19"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D26">
+    <sortCondition ref="D2:D26"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
